--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\Problemas Reactores Reales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\TFG Base Isabela Fons\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A975C3AE-23F2-4FBC-A061-4AEC172C759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E406E97-7175-44EF-9684-2844923FAA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="4830" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\TFG Base Isabela Fons\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E406E97-7175-44EF-9684-2844923FAA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C455A9-A60C-49B1-996C-8DA87F18A2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="4830" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="2340" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -376,10 +376,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>0</v>
@@ -402,10 +402,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -428,10 +428,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -454,10 +454,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -506,10 +506,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -532,10 +532,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -558,10 +558,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>40</v>
@@ -584,10 +584,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B11">
-        <v>2.2000000000000002</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>70</v>
@@ -636,10 +636,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B12">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -662,10 +662,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B13">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>125</v>
@@ -688,10 +688,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>150</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\TFG Base Isabela Fons\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C455A9-A60C-49B1-996C-8DA87F18A2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F143DB1B-E937-4040-A479-777569EDE438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2340" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\TFG Base Isabela Fons\ReactorApp toolbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F143DB1B-E937-4040-A479-777569EDE438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70D6994-F092-49BB-B3A9-151E697AD48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30180" yWindow="2700" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70D6994-F092-49BB-B3A9-151E697AD48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D742B5C-8D8C-41E3-A28D-4062F00664A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30180" yWindow="2700" windowWidth="15825" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -66,10 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -355,70 +369,87 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="2">
         <v>52</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="G1" s="1">
+      <c r="F1" s="2">
+        <v>52</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2">
         <v>54</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="K1" s="1">
+      <c r="I1" s="2">
+        <v>54</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2">
         <v>55</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="L1" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
+        <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,1)</f>
         <v>1</v>
       </c>
       <c r="B2">
+        <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,-1)</f>
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1">
+        <v>55</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
+        <f t="shared" ref="A3:A14" si="0">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,1)</f>
         <v>2</v>
       </c>
       <c r="B3">
+        <f t="shared" ref="B3:B14" si="1">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,-1)</f>
         <v>35</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>112</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
       <c r="K3">
         <v>1</v>
       </c>
@@ -428,23 +459,25 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4">
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>95.8</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
       <c r="K4">
         <v>2</v>
       </c>
@@ -454,21 +487,23 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5">
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>82.2</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>5</v>
       </c>
       <c r="K5">
@@ -480,21 +515,23 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6">
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>15</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>70.599999999999994</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>8</v>
       </c>
       <c r="K6">
@@ -506,21 +543,23 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7">
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>20</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>60.9</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>10</v>
       </c>
       <c r="K7">
@@ -532,21 +571,23 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B8">
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>30</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>45.6</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>8</v>
       </c>
       <c r="K8">
@@ -558,23 +599,25 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B9">
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>40</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>34.5</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
       <c r="K9">
         <v>8</v>
       </c>
@@ -584,21 +627,23 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B10">
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>50</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>26.3</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>4</v>
       </c>
       <c r="K10">
@@ -610,21 +655,23 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B11">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>70</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>15.7</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>8</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>3</v>
       </c>
       <c r="K11">
@@ -636,21 +683,23 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B12">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>100</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>7.67</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>9</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>2.2000000000000002</v>
       </c>
       <c r="K12">
@@ -662,21 +711,23 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B13">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>125</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>5.1100000000000003</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1.5</v>
       </c>
       <c r="K13">
@@ -688,21 +739,23 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>150</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>12</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.6</v>
       </c>
       <c r="K14">
@@ -713,16 +766,24 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D15">
+      <c r="A15" t="str">
+        <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1))</f>
+        <v/>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1))</f>
+        <v/>
+      </c>
+      <c r="E15">
         <v>175</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>1.73</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>14</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0</v>
       </c>
       <c r="K15">
@@ -733,19 +794,19 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D16">
+      <c r="E16">
         <v>200</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="K1:L1"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{8F165B2B-D0AA-4942-AF62-D2F5677EDBF9}">
+      <formula1>$D$1:$L$1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D742B5C-8D8C-41E3-A28D-4062F00664A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1123FD9-E97D-46BB-8B5F-DD34687E8D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -399,14 +399,14 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,-1)</f>
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="D2" s="1">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
@@ -432,11 +432,11 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" ref="A3:A14" si="0">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,1)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" si="1">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,-1)</f>
-        <v>35</v>
+        <v>95.8</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -460,11 +460,11 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>82.2</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -488,11 +488,11 @@
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -516,11 +516,11 @@
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>60.9</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -544,11 +544,11 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>45.6</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -572,11 +572,11 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>34.5</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -600,11 +600,11 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>26.3</v>
       </c>
       <c r="E9">
         <v>40</v>
@@ -628,11 +628,11 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>15.7</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -656,11 +656,11 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>7.67</v>
       </c>
       <c r="E11">
         <v>70</v>
@@ -684,11 +684,11 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -712,11 +712,11 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E13">
         <v>125</v>
@@ -740,11 +740,11 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="E14">
         <v>150</v>
@@ -766,13 +766,13 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
+      <c r="A15">
         <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1))</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>200</v>
+      </c>
+      <c r="B15">
         <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="E15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1123FD9-E97D-46BB-8B5F-DD34687E8D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AEBEC2-5AA0-4250-9C62-4B564C2E131A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5310" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -365,10 +365,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,8 +395,10 @@
       <c r="L1" s="2">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,1)</f>
         <v>0</v>
@@ -428,8 +430,10 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" ref="A3:A14" si="0">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,1)</f>
         <v>5</v>
@@ -457,7 +461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -485,7 +489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -513,7 +517,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -541,7 +545,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -569,7 +573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -597,7 +601,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -625,7 +629,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -653,7 +657,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>100</v>
@@ -681,7 +685,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -709,7 +713,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>150</v>
@@ -737,7 +741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>175</v>
@@ -765,7 +769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1))</f>
         <v>200</v>
@@ -793,7 +797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="E16">
         <v>200</v>
       </c>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AEBEC2-5AA0-4250-9C62-4B564C2E131A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E52B845-D134-4DDE-9E9E-9FCAA1FCB42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5310" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="2">
   <si>
     <t>t(min)</t>
   </si>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -395,8 +395,12 @@
       <c r="L1" s="2">
         <v>55</v>
       </c>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
+      <c r="N1" s="2">
+        <v>60</v>
+      </c>
+      <c r="O1" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -405,10 +409,10 @@
       </c>
       <c r="B2">
         <f>_xlfn.XLOOKUP($D$2,$1:$1,3:3,"no",0,-1)</f>
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
@@ -430,17 +434,21 @@
       <c r="L2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" ref="A3:A14" si="0">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,1)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" si="1">_xlfn.XLOOKUP($D$2,$1:$1,4:4,"no",0,-1)</f>
-        <v>95.8</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -459,16 +467,22 @@
       </c>
       <c r="L3">
         <v>9</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -487,16 +501,23 @@
       </c>
       <c r="L4">
         <v>35</v>
+      </c>
+      <c r="N4">
+        <f>+N3+1</f>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>70.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -515,16 +536,23 @@
       </c>
       <c r="L5">
         <v>52</v>
+      </c>
+      <c r="N5">
+        <f t="shared" ref="N5:N21" si="2">+N4+1</f>
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>60.9</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -543,16 +571,23 @@
       </c>
       <c r="L6">
         <v>65</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>45.6</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -571,16 +606,23 @@
       </c>
       <c r="L7">
         <v>82</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>34.5</v>
+        <v>190</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -599,16 +641,23 @@
       </c>
       <c r="L8">
         <v>77</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>26.3</v>
+        <v>161.5</v>
       </c>
       <c r="E9">
         <v>40</v>
@@ -627,16 +676,23 @@
       </c>
       <c r="L9">
         <v>70</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="O9">
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>123.5</v>
       </c>
       <c r="E10">
         <v>50</v>
@@ -655,16 +711,23 @@
       </c>
       <c r="L10">
         <v>56</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="O10">
+        <v>161.5</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>7.67</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>70</v>
@@ -683,16 +746,23 @@
       </c>
       <c r="L11">
         <v>47</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="O11">
+        <v>123.5</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>5.1100000000000003</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -711,16 +781,23 @@
       </c>
       <c r="L12">
         <v>32</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="O12">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>2.5499999999999998</v>
+        <v>58.9</v>
       </c>
       <c r="E13">
         <v>125</v>
@@ -739,16 +816,23 @@
       </c>
       <c r="L13">
         <v>15</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>1.73</v>
+        <v>43.7</v>
       </c>
       <c r="E14">
         <v>150</v>
@@ -767,16 +851,23 @@
       </c>
       <c r="L14">
         <v>7</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="O14">
+        <v>58.9</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,1))</f>
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,16:16,"no",0,-1))</f>
-        <v>0.9</v>
+        <v>20.9</v>
       </c>
       <c r="E15">
         <v>175</v>
@@ -796,19 +887,118 @@
       <c r="L15">
         <v>3</v>
       </c>
+      <c r="N15">
+        <f>+N14+1</f>
+        <v>12</v>
+      </c>
+      <c r="O15">
+        <v>43.7</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" ref="A16:A19" si="3">IF(_xlfn.XLOOKUP($D$2,$1:$1,17:17,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,17:17,"no",0,1))</f>
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:B19" si="4">IF(_xlfn.XLOOKUP($D$2,$1:$1,17:17,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,17:17,"no",0,-1))</f>
+        <v>7.6</v>
+      </c>
       <c r="E16">
         <v>200</v>
       </c>
       <c r="F16">
         <v>0.9</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="O16">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="4"/>
+        <v>1.9</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="O17">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="4"/>
+        <v>0.38</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="O18">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="4"/>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="O19">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,21:21,"no",0,1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,21:21,"no",0,1))</f>
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <f>IF(_xlfn.XLOOKUP($D$2,$1:$1,21:21,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$2,$1:$1,21:21,"no",0,-1))</f>
+        <v>1.9E-3</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="O20">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="O21">
+        <v>1.9E-3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{8F165B2B-D0AA-4942-AF62-D2F5677EDBF9}">
-      <formula1>$D$1:$L$1</formula1>
+      <formula1>$1:$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF851D53-C244-4E12-860B-424616A4265C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E53251-53B6-43E5-AA41-84FEFC92AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -439,12 +439,12 @@
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>1</v>
+        <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
+        <v>0</v>
       </c>
       <c r="B2">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>9</v>
+        <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -479,15 +479,15 @@
     </row>
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,4:4,"no",0,1)</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B3">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,4:4,"no",0,-1)</f>
-        <v>35</v>
+        <f t="shared" si="1"/>
+        <v>95.8</v>
       </c>
       <c r="D3" s="3">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -516,12 +516,12 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,5:5,"no",0,1)</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B4">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,5:5,"no",0,-1)</f>
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>82.2</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -551,12 +551,12 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,6:6,"no",0,1)</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B5">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,6:6,"no",0,-1)</f>
-        <v>65</v>
+        <f t="shared" si="1"/>
+        <v>70.599999999999994</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -577,7 +577,7 @@
         <v>52</v>
       </c>
       <c r="O5">
-        <f t="shared" ref="O5:O21" si="0">+O4+1</f>
+        <f t="shared" ref="O5:O21" si="2">+O4+1</f>
         <v>2</v>
       </c>
       <c r="P5">
@@ -586,12 +586,12 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,7:7,"no",0,1)</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B6">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,7:7,"no",0,-1)</f>
-        <v>82</v>
+        <f t="shared" si="1"/>
+        <v>60.9</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -612,7 +612,7 @@
         <v>65</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="P6">
@@ -621,12 +621,12 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,8:8,"no",0,1)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="B7">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,8:8,"no",0,-1)</f>
-        <v>77</v>
+        <f t="shared" si="1"/>
+        <v>45.6</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -647,7 +647,7 @@
         <v>82</v>
       </c>
       <c r="O7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="P7">
@@ -656,12 +656,12 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,9:9,"no",0,1)</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="B8">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,9:9,"no",0,-1)</f>
-        <v>70</v>
+        <f t="shared" si="1"/>
+        <v>34.5</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -682,7 +682,7 @@
         <v>77</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="P8">
@@ -691,12 +691,12 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,10:10,"no",0,1)</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="B9">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,10:10,"no",0,-1)</f>
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>26.3</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -717,7 +717,7 @@
         <v>70</v>
       </c>
       <c r="O9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="P9">
@@ -726,12 +726,12 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,11:11,"no",0,1)</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>70</v>
       </c>
       <c r="B10">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,11:11,"no",0,-1)</f>
-        <v>47</v>
+        <f t="shared" si="1"/>
+        <v>15.7</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -752,7 +752,7 @@
         <v>56</v>
       </c>
       <c r="O10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="P10">
@@ -761,12 +761,12 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,12:12,"no",0,1)</f>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="B11">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,12:12,"no",0,-1)</f>
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>7.67</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -787,7 +787,7 @@
         <v>47</v>
       </c>
       <c r="O11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="P11">
@@ -796,12 +796,12 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,13:13,"no",0,1)</f>
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>125</v>
       </c>
       <c r="B12">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,13:13,"no",0,-1)</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>5.1100000000000003</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -822,7 +822,7 @@
         <v>32</v>
       </c>
       <c r="O12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="P12">
@@ -831,12 +831,12 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,14:14,"no",0,1)</f>
-        <v>41</v>
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
       <c r="B13">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,14:14,"no",0,-1)</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -857,7 +857,7 @@
         <v>15</v>
       </c>
       <c r="O13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="P13">
@@ -866,12 +866,12 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,15:15,"no",0,1)</f>
-        <v>52</v>
+        <f t="shared" si="0"/>
+        <v>175</v>
       </c>
       <c r="B14">
-        <f>_xlfn.XLOOKUP($D$3,$1:$1,15:15,"no",0,-1)</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>1.73</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -892,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="P14">
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v/>
+      <c r="A15">
+        <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
+        <v>200</v>
+      </c>
+      <c r="B15">
+        <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
+        <v>0.9</v>
       </c>
       <c r="F15">
         <v>175</v>
@@ -936,11 +936,11 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,17:17,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,17:17,"no",0,1))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B16" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,17:17,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,17:17,"no",0,-1))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F16">
@@ -950,7 +950,7 @@
         <v>0.9</v>
       </c>
       <c r="O16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="P16">
@@ -959,15 +959,15 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,18:18,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,18:18,"no",0,1))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B17" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,18:18,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,18:18,"no",0,-1))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="P17">
@@ -976,15 +976,15 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,19:19,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,19:19,"no",0,1))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B18" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,19:19,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,19:19,"no",0,-1))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="P18">
@@ -993,15 +993,15 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,20:20,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,20:20,"no",0,1))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B19" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,20:20,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,20:20,"no",0,-1))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P19">
@@ -1010,15 +1010,15 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,21:21,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,21:21,"no",0,1))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="B20" t="str">
-        <f>IF(_xlfn.XLOOKUP($D$3,$1:$1,21:21,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,21:21,"no",0,-1))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="P20">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="O21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="P21">

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E53251-53B6-43E5-AA41-84FEFC92AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF920CA-E133-4337-86DF-BCABE1D7AB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>95.8</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>82.2</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>70.599999999999994</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>45.6</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>34.5</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>26.3</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>7.67</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>5.1100000000000003</v>
+        <v>15</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>2.5499999999999998</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" t="str">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v>200</v>
-      </c>
-      <c r="B15">
+        <v/>
+      </c>
+      <c r="B15" t="str">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v>0.9</v>
+        <v/>
       </c>
       <c r="F15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF920CA-E133-4337-86DF-BCABE1D7AB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED29E05-C129-42A5-BA80-81B0B7561476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>95.8</v>
       </c>
       <c r="D3" s="3">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>82.2</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>60.9</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>45.6</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>34.5</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>26.3</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>15.7</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>7.67</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
+      <c r="A15">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>200</v>
+      </c>
+      <c r="B15">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="F15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED29E05-C129-42A5-BA80-81B0B7561476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7D0043-0100-4CE0-AE37-389189B9BA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>95.8</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>82.2</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>70.599999999999994</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>45.6</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>34.5</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>26.3</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>7.67</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>5.1100000000000003</v>
+        <v>15</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>2.5499999999999998</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" t="str">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v>200</v>
-      </c>
-      <c r="B15">
+        <v/>
+      </c>
+      <c r="B15" t="str">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v>0.9</v>
+        <v/>
       </c>
       <c r="F15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7D0043-0100-4CE0-AE37-389189B9BA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF47478C-3C80-48CB-8631-5898CD1A81EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>95.8</v>
       </c>
       <c r="D3" s="3">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>82.2</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>60.9</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>45.6</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>34.5</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>26.3</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>15.7</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>7.67</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
+      <c r="A15">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>200</v>
+      </c>
+      <c r="B15">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="F15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF47478C-3C80-48CB-8631-5898CD1A81EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFE4D4A-D3CC-4A9B-AE72-4E699EDC434E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37635" yWindow="7155" windowWidth="18780" windowHeight="14220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>95.8</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>82.2</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>70.599999999999994</v>
+        <v>65</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>45.6</v>
+        <v>77</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>34.5</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>26.3</v>
+        <v>56</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>15.7</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>7.67</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>5.1100000000000003</v>
+        <v>15</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>2.5499999999999998</v>
+        <v>7</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" t="str">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v>200</v>
-      </c>
-      <c r="B15">
+        <v/>
+      </c>
+      <c r="B15" t="str">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v>0.9</v>
+        <v/>
       </c>
       <c r="F15">
         <v>175</v>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFE4D4A-D3CC-4A9B-AE72-4E699EDC434E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF36C61F-D2B9-4518-A278-7714565A15D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37635" yWindow="7155" windowWidth="18780" windowHeight="14220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32730" yWindow="6525" windowWidth="18780" windowHeight="14220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -440,11 +440,11 @@
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -480,14 +480,14 @@
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -517,11 +517,11 @@
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -552,11 +552,11 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -587,11 +587,11 @@
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -622,11 +622,11 @@
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -657,11 +657,11 @@
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -692,11 +692,11 @@
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>161.5</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -727,11 +727,11 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>123.5</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -762,11 +762,11 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -797,11 +797,11 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -832,11 +832,11 @@
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>58.9</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -867,11 +867,11 @@
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>43.7</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
+      <c r="A15">
         <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v/>
-      </c>
-      <c r="B15" t="str">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v/>
+        <v>20.9</v>
       </c>
       <c r="F15">
         <v>175</v>
@@ -935,13 +935,13 @@
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="str">
+      <c r="A16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B16" t="str">
+        <v>14</v>
+      </c>
+      <c r="B16">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7.6</v>
       </c>
       <c r="F16">
         <v>200</v>
@@ -958,13 +958,13 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="str">
+      <c r="A17">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B17" t="str">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.9</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
@@ -975,13 +975,13 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="str">
+      <c r="A18">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B18" t="str">
+        <v>16</v>
+      </c>
+      <c r="B18">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.38</v>
       </c>
       <c r="O18">
         <f t="shared" si="2"/>
@@ -992,13 +992,13 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="str">
+      <c r="A19">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B19" t="str">
+        <v>17</v>
+      </c>
+      <c r="B19">
         <f t="shared" si="4"/>
-        <v/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="O19">
         <f t="shared" si="2"/>
@@ -1009,13 +1009,13 @@
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="str">
+      <c r="A20">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B20" t="str">
+        <v>18</v>
+      </c>
+      <c r="B20">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.9E-3</v>
       </c>
       <c r="O20">
         <f t="shared" si="2"/>

--- a/Datos Problemas no ideales.xlsx
+++ b/Datos Problemas no ideales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFG\ReactorApp toolbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF36C61F-D2B9-4518-A278-7714565A15D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B0EF74-8274-4674-8068-13F57507E4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32730" yWindow="6525" windowWidth="18780" windowHeight="14220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
   <si>
     <t>t(min)</t>
   </si>
@@ -400,10 +400,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,15 +436,27 @@
       <c r="P1" s="2">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R1" s="2">
+        <v>62</v>
+      </c>
+      <c r="S1" s="2">
+        <v>62</v>
+      </c>
+      <c r="U1" s="2">
+        <v>64</v>
+      </c>
+      <c r="V1" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <f t="shared" ref="A2:A14" si="0">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,1)</f>
         <v>0</v>
       </c>
       <c r="B2">
         <f t="shared" ref="B2:B14" si="1">_xlfn.XLOOKUP($D$3,$1:$1,3:3,"no",0,-1)</f>
-        <v>0</v>
+        <v>15.37</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>2</v>
@@ -476,18 +488,30 @@
       <c r="P2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="B3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="D3" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -513,15 +537,27 @@
       <c r="P3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="B4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.15</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -548,15 +584,27 @@
       <c r="P4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>0.5</v>
+      </c>
+      <c r="S4">
+        <v>60</v>
+      </c>
+      <c r="U4">
+        <v>0.4</v>
+      </c>
+      <c r="V4">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="B5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.93</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -583,15 +631,27 @@
       <c r="P5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>70</v>
+      </c>
+      <c r="U5">
+        <v>0.8</v>
+      </c>
+      <c r="V5">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="B6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="F6">
         <v>15</v>
@@ -618,15 +678,27 @@
       <c r="P6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <v>1.5</v>
+      </c>
+      <c r="S6">
+        <v>86</v>
+      </c>
+      <c r="U6">
+        <v>1.2</v>
+      </c>
+      <c r="V6">
+        <v>11.93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -653,15 +725,27 @@
       <c r="P7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>91</v>
+      </c>
+      <c r="U7">
+        <v>1.6</v>
+      </c>
+      <c r="V7">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="B8">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>7.59</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -688,15 +772,27 @@
       <c r="P8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R8">
+        <v>2.5</v>
+      </c>
+      <c r="S8">
+        <v>84</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="B9">
         <f t="shared" si="1"/>
-        <v>161.5</v>
+        <v>7.46</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -723,15 +819,27 @@
       <c r="P9">
         <v>190</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9">
+        <v>78</v>
+      </c>
+      <c r="U9">
+        <v>2.4</v>
+      </c>
+      <c r="V9">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="B10">
         <f t="shared" si="1"/>
-        <v>123.5</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -758,15 +866,27 @@
       <c r="P10">
         <v>161.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R10">
+        <v>3.5</v>
+      </c>
+      <c r="S10">
+        <v>76</v>
+      </c>
+      <c r="U10">
+        <v>2.8</v>
+      </c>
+      <c r="V10">
+        <v>7.46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>5.24</v>
       </c>
       <c r="F11">
         <v>70</v>
@@ -793,15 +913,27 @@
       <c r="P11">
         <v>123.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="S11">
+        <v>67</v>
+      </c>
+      <c r="U11">
+        <v>3.2</v>
+      </c>
+      <c r="V11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="B12">
         <f t="shared" si="1"/>
-        <v>76</v>
+        <v>3.75</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -828,15 +960,27 @@
       <c r="P12">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R12">
+        <v>4.5</v>
+      </c>
+      <c r="S12">
+        <v>57</v>
+      </c>
+      <c r="U12">
+        <v>4</v>
+      </c>
+      <c r="V12">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="B13">
         <f t="shared" si="1"/>
-        <v>58.9</v>
+        <v>3.27</v>
       </c>
       <c r="F13">
         <v>125</v>
@@ -863,15 +1007,27 @@
       <c r="P13">
         <v>76</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R13">
+        <v>5</v>
+      </c>
+      <c r="S13">
+        <v>47</v>
+      </c>
+      <c r="U13">
+        <v>4.8</v>
+      </c>
+      <c r="V13">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="B14">
         <f t="shared" si="1"/>
-        <v>43.7</v>
+        <v>2.08</v>
       </c>
       <c r="F14">
         <v>150</v>
@@ -898,15 +1054,27 @@
       <c r="P14">
         <v>58.9</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R14">
+        <v>6</v>
+      </c>
+      <c r="S14">
+        <v>36</v>
+      </c>
+      <c r="U14">
+        <v>5.6</v>
+      </c>
+      <c r="V14">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" ref="A15:A20" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
-        <v>13</v>
+        <f t="shared" ref="A15:A23" si="3">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,1))</f>
+        <v>8</v>
       </c>
       <c r="B15">
-        <f t="shared" ref="B15:B20" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
-        <v>20.9</v>
+        <f t="shared" ref="B15:B23" si="4">IF(_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1)=0,"",_xlfn.XLOOKUP($D$3,$1:$1,16:16,"no",0,-1))</f>
+        <v>1.62</v>
       </c>
       <c r="F15">
         <v>175</v>
@@ -933,15 +1101,27 @@
       <c r="P15">
         <v>43.7</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R15">
+        <v>7</v>
+      </c>
+      <c r="S15">
+        <v>25</v>
+      </c>
+      <c r="U15">
+        <v>5.8</v>
+      </c>
+      <c r="V15">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="B16">
         <f t="shared" si="4"/>
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="F16">
         <v>200</v>
@@ -956,15 +1136,27 @@
       <c r="P16">
         <v>20.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R16">
+        <v>9</v>
+      </c>
+      <c r="S16">
+        <v>12</v>
+      </c>
+      <c r="U16">
+        <v>8</v>
+      </c>
+      <c r="V16">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>10.8</v>
       </c>
       <c r="B17">
         <f t="shared" si="4"/>
-        <v>1.9</v>
+        <v>0.71</v>
       </c>
       <c r="O17">
         <f t="shared" si="2"/>
@@ -973,15 +1165,27 @@
       <c r="P17">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R17">
+        <v>11</v>
+      </c>
+      <c r="S17">
+        <v>5.7</v>
+      </c>
+      <c r="U17">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="V17">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>12.8</v>
       </c>
       <c r="B18">
         <f t="shared" si="4"/>
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="O18">
         <f t="shared" si="2"/>
@@ -990,15 +1194,27 @@
       <c r="P18">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>13</v>
+      </c>
+      <c r="S18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="U18">
+        <v>10.8</v>
+      </c>
+      <c r="V18">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="B19">
         <f t="shared" si="4"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.12</v>
       </c>
       <c r="O19">
         <f t="shared" si="2"/>
@@ -1007,15 +1223,27 @@
       <c r="P19">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R19">
+        <v>15</v>
+      </c>
+      <c r="S19">
+        <v>0.98</v>
+      </c>
+      <c r="U19">
+        <v>12.8</v>
+      </c>
+      <c r="V19">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>20.8</v>
       </c>
       <c r="B20">
         <f t="shared" si="4"/>
-        <v>1.9E-3</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="O20">
         <f t="shared" si="2"/>
@@ -1024,14 +1252,92 @@
       <c r="P20">
         <v>9.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R20">
+        <v>17</v>
+      </c>
+      <c r="S20">
+        <v>0.43</v>
+      </c>
+      <c r="U20">
+        <v>16.8</v>
+      </c>
+      <c r="V20">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="4"/>
+        <v>1E-3</v>
+      </c>
       <c r="O21">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="P21">
         <v>1.9E-3</v>
+      </c>
+      <c r="R21">
+        <v>19</v>
+      </c>
+      <c r="S21">
+        <v>0.16</v>
+      </c>
+      <c r="U21">
+        <v>20.8</v>
+      </c>
+      <c r="V21">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R22">
+        <v>21</v>
+      </c>
+      <c r="S22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U22">
+        <v>24</v>
+      </c>
+      <c r="V22">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="R23">
+        <v>23</v>
+      </c>
+      <c r="S23">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>25</v>
+      </c>
+      <c r="S24">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
